--- a/セリフ編集/その他セリフ/06-契約交渉.xlsx
+++ b/セリフ編集/その他セリフ/06-契約交渉.xlsx
@@ -192,7 +192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I177"/>
+  <dimension ref="A1:I197"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -4521,7 +4521,7 @@
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted.ojousama[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4536,19 +4536,24 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.introverted._default[1]</t>
+          <t xml:space="preserve">sudden_departure.introverted.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すみません。もう、限界なんです。……さようなら。</t>
+          <t xml:space="preserve">……申し訳ありません。もう、限界ですの。……ごきげんよう。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted._default[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted.ojousama[2]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4563,19 +4568,24 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.introverted._default[2]</t>
+          <t xml:space="preserve">sudden_departure.introverted.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ずっと我慢してきたんです。でも、もう……。</t>
+          <t xml:space="preserve">……ずっと堪えてまいりました。ですが、もう……。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted._default[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted.delinquent[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4590,19 +4600,24 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.introverted._default[3]</t>
+          <t xml:space="preserve">sudden_departure.introverted.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……何も言わずに去ろうかと思ったけど、一応挨拶だけ。辞めます。</t>
+          <t xml:space="preserve">……すんません。もう、限界っす。……さよなら。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted.delinquent[2]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4617,24 +4632,24 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.introverted.polite[1]</t>
+          <t xml:space="preserve">sudden_departure.introverted.delinquent[2]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……お忙しいところすみません。退団届を、出させてください。</t>
+          <t xml:space="preserve">……黙って出てこうかと思ったんすけど。一応、挨拶だけ。辞めます。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted.polite[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted.cool[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4649,24 +4664,24 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.introverted.polite[2]</t>
+          <t xml:space="preserve">sudden_departure.introverted.cool[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……色々考えたんですけど、もう続けられません。すみません。</t>
+          <t xml:space="preserve">……すみません。……もう、限界です</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted.cool[2]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4681,19 +4696,24 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.carefree._default[1]</t>
+          <t xml:space="preserve">sudden_departure.introverted.cool[2]</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー、ついにこの日が来ちゃいましたね。じゃ、元気で。</t>
+          <t xml:space="preserve">……黙って消えようかと思った。……一応、挨拶だけ</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree._default[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted.seductive[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4708,19 +4728,24 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.carefree._default[2]</t>
+          <t xml:space="preserve">sudden_departure.introverted.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう潮時かなって。楽しかったですよ、うん。じゃあね！</t>
+          <t xml:space="preserve">……ごめんなさい。もう、限界なの。……さようなら。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree._default[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted.seductive[2]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4735,19 +4760,24 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.carefree._default[3]</t>
+          <t xml:space="preserve">sudden_departure.introverted.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、もう笑うしかないですよね。辞めまーす。</t>
+          <t xml:space="preserve">……ずっと黙って耐えてきたわ。でも、もう……。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted.composed[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4762,24 +4792,24 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.carefree.seductive[1]</t>
+          <t xml:space="preserve">sudden_departure.introverted.composed[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、もう引き止めないでくださいね？ 決めちゃったんですから。</t>
+          <t xml:space="preserve">……すみません。…もう、限界でね。…さようなら。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree.seductive[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted.composed[2]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4794,24 +4824,24 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.carefree.seductive[2]</t>
+          <t xml:space="preserve">sudden_departure.introverted.composed[2]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さよなら、社長。楽しかった時もあったわ。</t>
+          <t xml:space="preserve">…黙って出ていこうかと思ったけど。…一応、挨拶だけ。辞めます。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted._default[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4826,24 +4856,19 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.earnest._default[1]</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">sudden_departure.introverted._default[1]</t>
         </is>
       </c>
       <c r="G146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、長い間お世話になりました。でも、もうここでは続けられません。</t>
+          <t xml:space="preserve">……すみません。もう、限界なんです。……さようなら。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest._default[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted._default[2]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4858,24 +4883,19 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.earnest._default[2]</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">sudden_departure.introverted._default[2]</t>
         </is>
       </c>
       <c r="G147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">自分なりにずっと考えてきました。……ここを去ることにします。</t>
+          <t xml:space="preserve">……ずっと我慢してきたんです。でも、もう……。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest._default[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted._default[3]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -4890,24 +4910,19 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.earnest._default[3]</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">sudden_departure.introverted._default[3]</t>
         </is>
       </c>
       <c r="G148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これ以上、自分を偽って続けることはできません。退団させてください。</t>
+          <t xml:space="preserve">……何も言わずに去ろうかと思ったけど、一応挨拶だけ。辞めます。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.emotional._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted.polite[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -4922,24 +4937,24 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.emotional._default[1]</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">sudden_departure.introverted.polite[1]</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もういいです。もう何も言いたくない。……さよなら。</t>
+          <t xml:space="preserve">……お忙しいところすみません。退団届を、出させてください。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.emotional._default[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted.polite[2]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -4954,24 +4969,24 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.emotional._default[2]</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">sudden_departure.introverted.polite[2]</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんで……なんでこんなことになったんですか。もう無理です、辞めます。</t>
+          <t xml:space="preserve">……色々考えたんですけど、もう続けられません。すみません。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.emotional._default[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree.ojousama[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -4986,24 +5001,24 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.emotional._default[3]</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">sudden_departure.carefree.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい……悔しいけど、もうここにはいられない。</t>
+          <t xml:space="preserve">まあ、とうとうこの日が参りましたのね。では、お元気で。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.shy._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree.ojousama[2]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5018,24 +5033,24 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.shy._default[1]</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">sudden_departure.carefree.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの、辞め……辞めさせてください……。もう、無理なんです……。</t>
+          <t xml:space="preserve">そろそろ潮時かしら。楽しゅうございました、ええ。ごきげんよう。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.shy._default[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree.delinquent[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5050,24 +5065,24 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.shy._default[2]</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">sudden_departure.carefree.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめんなさい。もう、ここにはいられません……。</t>
+          <t xml:space="preserve">いやー、ついにこの日が来ちまったっすね。じゃ、元気で。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree.delinquent[2]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5082,24 +5097,24 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.normal._default[1]</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">sudden_departure.carefree.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、話は短く済ませます。辞めます。もう決めました。</t>
+          <t xml:space="preserve">もう潮時っしょ。楽しかったっすよ、うん。じゃあ、失礼します。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal._default[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree.cool[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5114,24 +5129,24 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.normal._default[2]</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">sudden_departure.carefree.cool[1]</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お世話になりました。でも、もうここでは続けられません。</t>
+          <t xml:space="preserve">……ついに、この日か。……じゃ、元気で</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal._default[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree.cool[2]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5146,24 +5161,24 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.normal._default[3]</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">sudden_departure.carefree.cool[2]</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">色々ありましたけど……もう、終わりにします。</t>
+          <t xml:space="preserve">…潮時だ。楽しかったよ。……辞めます</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree.polite[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5173,29 +5188,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed[1]</t>
+          <t xml:space="preserve">sudden_departure.carefree.polite[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……短い間だったけど、悪くない時間だった。ありがとう。</t>
+          <t xml:space="preserve">いやー、ついにこの日が来てしまいましたね。では、お元気で。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.composed[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree.polite[2]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5205,29 +5220,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed[2]</t>
+          <t xml:space="preserve">sudden_departure.carefree.polite[2]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、こういうこともあるよね。……元気でね、社長。</t>
+          <t xml:space="preserve">もう潮時かなと思いまして。楽しかったですよ、ええ。失礼します！</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.composed[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree.composed[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5237,12 +5252,12 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed[3]</t>
+          <t xml:space="preserve">sudden_departure.carefree.composed[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5252,14 +5267,14 @@
       </c>
       <c r="G159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……わかった。世話になったよ。次の場所、自分で見つけるから。</t>
+          <t xml:space="preserve">…いやあ、ついにこの日が来たね。…じゃ、元気で。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree.composed[2]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5269,29 +5284,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama[1]</t>
+          <t xml:space="preserve">sudden_departure.carefree.composed[2]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご縁がここまでだったということですわね。お世話になりました。</t>
+          <t xml:space="preserve">…潮時かなって。楽しかったよ、うん。…じゃあね。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.ojousama[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree._default[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5301,29 +5316,24 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama[2]</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">sudden_departure.carefree._default[1]</t>
         </is>
       </c>
       <c r="G161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……承知いたしましたわ。これまでのご厚情、忘れませんわ。</t>
+          <t xml:space="preserve">いやー、ついにこの日が来ちゃいましたね。じゃ、元気で。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.ojousama[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree._default[2]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5333,29 +5343,24 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama[3]</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">sudden_departure.carefree._default[2]</t>
         </is>
       </c>
       <c r="G162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの居場所は、また別にございますわ。社長もお元気で。</t>
+          <t xml:space="preserve">もう潮時かなって。楽しかったですよ、うん。じゃあね！</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree._default[3]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5365,29 +5370,24 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite[1]</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">sudden_departure.carefree._default[3]</t>
         </is>
       </c>
       <c r="G163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">至らない点があったなら、申し訳ありませんでした。今までご指導ありがとうございました。</t>
+          <t xml:space="preserve">あはは、もう笑うしかないですよね。辞めまーす。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.polite[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree.seductive[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5397,29 +5397,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite[2]</t>
+          <t xml:space="preserve">sudden_departure.carefree.seductive[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">力不足でした。……この経験を、次に必ず活かさせていただきます。</t>
+          <t xml:space="preserve">ふふ、もう引き止めないでくださいね？ 決めちゃったんですから。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.polite[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree.seductive[2]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5429,29 +5429,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite[3]</t>
+          <t xml:space="preserve">sudden_departure.carefree.seductive[2]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お世話になりました。社長も、団体の皆様も、どうかお元気で。</t>
+          <t xml:space="preserve">さよなら、社長。楽しかった時もあったわ。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest._default[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5461,29 +5461,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive[1]</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">sudden_departure.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、寂しいことを仰るのね。……ふふ、いいわ、潔く出ていきましょう。</t>
+          <t xml:space="preserve">社長、長い間お世話になりました。でも、もうここでは続けられません。</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.seductive[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest._default[2]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5493,29 +5493,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive[2]</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">sudden_departure.earnest._default[2]</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">別れって、嫌いじゃないの。……お世話になったわ、社長。</t>
+          <t xml:space="preserve">自分なりにずっと考えてきました。……ここを去ることにします。</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.seductive[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest._default[3]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5525,29 +5525,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive[3]</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">sudden_departure.earnest._default[3]</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">またどこかで会えるかしら。……忘れないでね、私のこと。</t>
+          <t xml:space="preserve">これ以上、自分を偽って続けることはできません。退団させてください。</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.emotional._default[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5557,29 +5557,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">sudden_departure.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チッ……悔しいけど、次はもっといい場所で暴れてやるよ。見てな。</t>
+          <t xml:space="preserve">もういいです。もう何も言いたくない。……さよなら。</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.delinquent[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.emotional._default[2]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5589,29 +5589,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent[2]</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">sudden_departure.emotional._default[2]</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こうなったらどこ行っても結果出すからな。覚えとけよ社長。</t>
+          <t xml:space="preserve">なんで……なんでこんなことになったんですか。もう無理です、辞めます。</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.delinquent[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.emotional._default[3]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5621,29 +5621,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent[3]</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">sudden_departure.emotional._default[3]</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……わかったよ。この悔しさ、絶対に忘れねぇからな。</t>
+          <t xml:space="preserve">悔しい……悔しいけど、もうここにはいられない。</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.shy._default[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5653,29 +5653,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool[1]</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">sudden_departure.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……わかった。</t>
+          <t xml:space="preserve">……あの、辞め……辞めさせてください……。もう、無理なんです……。</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.cool[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.shy._default[2]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5685,29 +5685,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool[2]</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">sudden_departure.shy._default[2]</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……世話になった。</t>
+          <t xml:space="preserve">……ごめんなさい。もう、ここにはいられません……。</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.cool[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal._default[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5717,29 +5717,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool[3]</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">sudden_departure.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次の場所で、結果を出す。</t>
+          <t xml:space="preserve">社長、話は短く済ませます。辞めます。もう決めました。</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.normal[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal._default[2]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal[1]</t>
+          <t xml:space="preserve">sudden_departure.normal._default[2]</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="5">
@@ -5764,14 +5764,14 @@
       </c>
       <c r="G175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間でしたが、ありがとうございました。</t>
+          <t xml:space="preserve">お世話になりました。でも、もうここでは続けられません。</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.normal[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal._default[3]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal[2]</t>
+          <t xml:space="preserve">sudden_departure.normal._default[3]</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="5">
@@ -5796,44 +5796,684 @@
       </c>
       <c r="G176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">色々と、お世話になりました。……お元気で。</t>
+          <t xml:space="preserve">色々ありましたけど……もう、終わりにします。</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.composed[1]</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed[1]</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……短い間だったけど、悪くない時間だった。ありがとう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="40" customHeight="1">
+      <c r="A178" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.composed[2]</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed[2]</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ま、こういうこともあるよね。……元気でね、社長。</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="40" customHeight="1">
+      <c r="A179" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.composed[3]</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed[3]</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……わかった。世話になったよ。次の場所、自分で見つけるから。</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="40" customHeight="1">
+      <c r="A180" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ご縁がここまでだったということですわね。お世話になりました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="40" customHeight="1">
+      <c r="A181" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……承知いたしましたわ。これまでのご厚情、忘れませんわ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="40" customHeight="1">
+      <c r="A182" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.ojousama[3]</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama[3]</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたくしの居場所は、また別にございますわ。社長もお元気で。</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="40" customHeight="1">
+      <c r="A183" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.polite[1]</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite[1]</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">至らない点があったなら、申し訳ありませんでした。今までご指導ありがとうございました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="40" customHeight="1">
+      <c r="A184" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.polite[2]</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite[2]</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">力不足でした。……この経験を、次に必ず活かさせていただきます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="40" customHeight="1">
+      <c r="A185" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.polite[3]</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite[3]</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お世話になりました。社長も、団体の皆様も、どうかお元気で。</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="40" customHeight="1">
+      <c r="A186" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive[1]</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、寂しいことを仰るのね。……ふふ、いいわ、潔く出ていきましょう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="40" customHeight="1">
+      <c r="A187" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive[2]</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">別れって、嫌いじゃないの。……お世話になったわ、社長。</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="40" customHeight="1">
+      <c r="A188" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.seductive[3]</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive[3]</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">またどこかで会えるかしら。……忘れないでね、私のこと。</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="40" customHeight="1">
+      <c r="A189" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">チッ……悔しいけど、次はもっといい場所で暴れてやるよ。見てな。</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="40" customHeight="1">
+      <c r="A190" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">こうなったらどこ行っても結果出すからな。覚えとけよ社長。</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="40" customHeight="1">
+      <c r="A191" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.delinquent[3]</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent[3]</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……わかったよ。この悔しさ、絶対に忘れねぇからな。</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="40" customHeight="1">
+      <c r="A192" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.cool[1]</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool[1]</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……わかった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="40" customHeight="1">
+      <c r="A193" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.cool[2]</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool[2]</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……世話になった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="40" customHeight="1">
+      <c r="A194" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.cool[3]</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool[3]</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……次の場所で、結果を出す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="40" customHeight="1">
+      <c r="A195" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.normal[1]</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal[1]</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">短い間でしたが、ありがとうございました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="40" customHeight="1">
+      <c r="A196" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.normal[2]</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">normal[2]</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">色々と、お世話になりました。……お元気で。</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="40" customHeight="1">
+      <c r="A197" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">RELEASE_INTERVIEW_LINES.normal[3]</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr" s="2">
+      <c r="B197" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr" s="12">
+      <c r="D197" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">normal[3]</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr" s="5">
+      <c r="F197" t="inlineStr" s="5">
         <is>
           <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr" s="3">
+      <c r="G197" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">これからも、この団体の活躍、祈ってます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I177"/>
+  <autoFilter ref="A1:I197"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/その他セリフ/06-契約交渉.xlsx
+++ b/セリフ編集/その他セリフ/06-契約交渉.xlsx
@@ -6379,7 +6379,7 @@
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.normal[1]</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.standard[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal[1]</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">standard[1]</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G195" t="inlineStr" s="3">
@@ -6411,7 +6411,7 @@
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.normal[2]</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.standard[2]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal[2]</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">standard[2]</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G196" t="inlineStr" s="3">
@@ -6443,7 +6443,7 @@
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.normal[3]</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.standard[3]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal[3]</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">standard[3]</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G197" t="inlineStr" s="3">

--- a/セリフ編集/その他セリフ/06-契約交渉.xlsx
+++ b/セリフ編集/その他セリフ/06-契約交渉.xlsx
@@ -192,7 +192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I197"/>
+  <dimension ref="A1:I173"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -256,7 +256,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.normal._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start._default.normal[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -271,7 +271,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.normal._default[1]</t>
+          <t xml:space="preserve">start._default.normal[1]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="5">
@@ -289,7 +289,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.bold._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start._default.bold[1]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -304,7 +304,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.bold._default[1]</t>
+          <t xml:space="preserve">start._default.bold[1]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr" s="6">
@@ -322,7 +322,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.bold._default[2]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start._default.bold[2]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -337,7 +337,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.bold._default[2]</t>
+          <t xml:space="preserve">start._default.bold[2]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr" s="6">
@@ -355,7 +355,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.quiet._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start._default.quiet[1]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -370,7 +370,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.quiet._default[1]</t>
+          <t xml:space="preserve">start._default.quiet[1]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr" s="7">
@@ -387,7 +387,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.shy._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start._default.shy[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -402,7 +402,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.shy._default[1]</t>
+          <t xml:space="preserve">start._default.shy[1]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="8">
@@ -420,7 +420,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.easygoing._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -435,7 +435,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.easygoing._default[1]</t>
+          <t xml:space="preserve">start._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr" s="9">
@@ -453,7 +453,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.earnest._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start._default.earnest[1]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -468,7 +468,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.earnest._default[1]</t>
+          <t xml:space="preserve">start._default.earnest[1]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="10">
@@ -486,7 +486,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.emotional._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start._default.emotional[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -501,7 +501,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.emotional._default[1]</t>
+          <t xml:space="preserve">start._default.emotional[1]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="10">
@@ -519,7 +519,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.normal._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success._default.normal[1]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -534,7 +534,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.normal._default[1]</t>
+          <t xml:space="preserve">success._default.normal[1]</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="5">
@@ -552,7 +552,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.bold._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success._default.bold[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -567,7 +567,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.bold._default[1]</t>
+          <t xml:space="preserve">success._default.bold[1]</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="6">
@@ -585,7 +585,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.bold._default[2]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success._default.bold[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -600,7 +600,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.bold._default[2]</t>
+          <t xml:space="preserve">success._default.bold[2]</t>
         </is>
       </c>
       <c r="F12" t="inlineStr" s="6">
@@ -618,7 +618,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.quiet._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success._default.quiet[1]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -633,7 +633,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.quiet._default[1]</t>
+          <t xml:space="preserve">success._default.quiet[1]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="7">
@@ -650,7 +650,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.shy._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success._default.shy[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -665,7 +665,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.shy._default[1]</t>
+          <t xml:space="preserve">success._default.shy[1]</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="8">
@@ -683,7 +683,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.easygoing._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -698,7 +698,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.easygoing._default[1]</t>
+          <t xml:space="preserve">success._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="9">
@@ -716,7 +716,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.earnest._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success._default.earnest[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -731,7 +731,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.earnest._default[1]</t>
+          <t xml:space="preserve">success._default.earnest[1]</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="10">
@@ -749,7 +749,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.emotional._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success._default.emotional[1]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -764,7 +764,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.emotional._default[1]</t>
+          <t xml:space="preserve">success._default.emotional[1]</t>
         </is>
       </c>
       <c r="F17" t="inlineStr" s="10">
@@ -782,7 +782,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.normal._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked._default.normal[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -797,7 +797,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.normal._default[1]</t>
+          <t xml:space="preserve">blocked._default.normal[1]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr" s="5">
@@ -815,7 +815,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.normal._default[2]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked._default.normal[2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -830,7 +830,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.normal._default[2]</t>
+          <t xml:space="preserve">blocked._default.normal[2]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr" s="5">
@@ -848,7 +848,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.bold._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked._default.bold[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -863,7 +863,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.bold._default[1]</t>
+          <t xml:space="preserve">blocked._default.bold[1]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="6">
@@ -881,7 +881,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.bold._default[2]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked._default.bold[2]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -896,7 +896,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.bold._default[2]</t>
+          <t xml:space="preserve">blocked._default.bold[2]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="6">
@@ -914,7 +914,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.quiet._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked._default.quiet[1]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -929,7 +929,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.quiet._default[1]</t>
+          <t xml:space="preserve">blocked._default.quiet[1]</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="7">
@@ -946,7 +946,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.shy._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked._default.shy[1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -961,7 +961,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.shy._default[1]</t>
+          <t xml:space="preserve">blocked._default.shy[1]</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="8">
@@ -979,7 +979,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.easygoing._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -994,7 +994,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.easygoing._default[1]</t>
+          <t xml:space="preserve">blocked._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F24" t="inlineStr" s="9">
@@ -1012,7 +1012,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.easygoing._default[2]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.easygoing._default[2]</t>
+          <t xml:space="preserve">blocked._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="9">
@@ -1045,7 +1045,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.earnest._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked._default.earnest[1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.earnest._default[1]</t>
+          <t xml:space="preserve">blocked._default.earnest[1]</t>
         </is>
       </c>
       <c r="F26" t="inlineStr" s="10">
@@ -1078,7 +1078,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.earnest._default[2]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked._default.earnest[2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.earnest._default[2]</t>
+          <t xml:space="preserve">blocked._default.earnest[2]</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="10">
@@ -1111,7 +1111,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.emotional._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked._default.emotional[1]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.emotional._default[1]</t>
+          <t xml:space="preserve">blocked._default.emotional[1]</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="10">
@@ -1144,7 +1144,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.emotional._default[2]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked._default.emotional[2]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.emotional._default[2]</t>
+          <t xml:space="preserve">blocked._default.emotional[2]</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="10">
@@ -1177,7 +1177,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.normal._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail._default.normal[1]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.normal._default[1]</t>
+          <t xml:space="preserve">fail._default.normal[1]</t>
         </is>
       </c>
       <c r="F30" t="inlineStr" s="5">
@@ -1210,7 +1210,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.bold._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail._default.bold[1]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.bold._default[1]</t>
+          <t xml:space="preserve">fail._default.bold[1]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="6">
@@ -1243,7 +1243,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.bold._default[2]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail._default.bold[2]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.bold._default[2]</t>
+          <t xml:space="preserve">fail._default.bold[2]</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="6">
@@ -1276,7 +1276,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.quiet._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail._default.quiet[1]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.quiet._default[1]</t>
+          <t xml:space="preserve">fail._default.quiet[1]</t>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="7">
@@ -1308,7 +1308,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.shy._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail._default.shy[1]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.shy._default[1]</t>
+          <t xml:space="preserve">fail._default.shy[1]</t>
         </is>
       </c>
       <c r="F34" t="inlineStr" s="8">
@@ -1341,7 +1341,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.easygoing._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.easygoing._default[1]</t>
+          <t xml:space="preserve">fail._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F35" t="inlineStr" s="9">
@@ -1374,7 +1374,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.earnest._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail._default.earnest[1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.earnest._default[1]</t>
+          <t xml:space="preserve">fail._default.earnest[1]</t>
         </is>
       </c>
       <c r="F36" t="inlineStr" s="10">
@@ -1407,7 +1407,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.emotional._default[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail._default.emotional[1]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.emotional._default[1]</t>
+          <t xml:space="preserve">fail._default.emotional[1]</t>
         </is>
       </c>
       <c r="F37" t="inlineStr" s="10">
@@ -1440,7 +1440,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.normal._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open._default.normal[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.normal._default[1]</t>
+          <t xml:space="preserve">raise_open._default.normal[1]</t>
         </is>
       </c>
       <c r="F38" t="inlineStr" s="5">
@@ -1472,7 +1472,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.normal._default[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open._default.normal[2]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.normal._default[2]</t>
+          <t xml:space="preserve">raise_open._default.normal[2]</t>
         </is>
       </c>
       <c r="F39" t="inlineStr" s="5">
@@ -1504,7 +1504,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.bold._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open._default.bold[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.bold._default[1]</t>
+          <t xml:space="preserve">raise_open._default.bold[1]</t>
         </is>
       </c>
       <c r="F40" t="inlineStr" s="6">
@@ -1536,7 +1536,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.bold._default[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open._default.bold[2]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.bold._default[2]</t>
+          <t xml:space="preserve">raise_open._default.bold[2]</t>
         </is>
       </c>
       <c r="F41" t="inlineStr" s="6">
@@ -1568,7 +1568,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.quiet._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open._default.quiet[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.quiet._default[1]</t>
+          <t xml:space="preserve">raise_open._default.quiet[1]</t>
         </is>
       </c>
       <c r="F42" t="inlineStr" s="7">
@@ -1600,7 +1600,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.quiet._default[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open._default.quiet[2]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.quiet._default[2]</t>
+          <t xml:space="preserve">raise_open._default.quiet[2]</t>
         </is>
       </c>
       <c r="F43" t="inlineStr" s="7">
@@ -1632,7 +1632,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.shy._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open._default.shy[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.shy._default[1]</t>
+          <t xml:space="preserve">raise_open._default.shy[1]</t>
         </is>
       </c>
       <c r="F44" t="inlineStr" s="8">
@@ -1664,7 +1664,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.shy._default[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open._default.shy[2]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.shy._default[2]</t>
+          <t xml:space="preserve">raise_open._default.shy[2]</t>
         </is>
       </c>
       <c r="F45" t="inlineStr" s="8">
@@ -1696,7 +1696,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.easygoing._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.easygoing._default[1]</t>
+          <t xml:space="preserve">raise_open._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F46" t="inlineStr" s="9">
@@ -1728,7 +1728,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.easygoing._default[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.easygoing._default[2]</t>
+          <t xml:space="preserve">raise_open._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F47" t="inlineStr" s="9">
@@ -1760,7 +1760,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.earnest._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open._default.earnest[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.earnest._default[1]</t>
+          <t xml:space="preserve">raise_open._default.earnest[1]</t>
         </is>
       </c>
       <c r="F48" t="inlineStr" s="10">
@@ -1792,7 +1792,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.earnest._default[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open._default.earnest[2]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.earnest._default[2]</t>
+          <t xml:space="preserve">raise_open._default.earnest[2]</t>
         </is>
       </c>
       <c r="F49" t="inlineStr" s="10">
@@ -1824,7 +1824,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.emotional._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open._default.emotional[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.emotional._default[1]</t>
+          <t xml:space="preserve">raise_open._default.emotional[1]</t>
         </is>
       </c>
       <c r="F50" t="inlineStr" s="10">
@@ -1856,7 +1856,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.emotional._default[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open._default.emotional[2]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.emotional._default[2]</t>
+          <t xml:space="preserve">raise_open._default.emotional[2]</t>
         </is>
       </c>
       <c r="F51" t="inlineStr" s="10">
@@ -1888,7 +1888,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.normal._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open._default.normal[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.normal._default[1]</t>
+          <t xml:space="preserve">transfer_open._default.normal[1]</t>
         </is>
       </c>
       <c r="F52" t="inlineStr" s="5">
@@ -1920,7 +1920,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.normal._default[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open._default.normal[2]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.normal._default[2]</t>
+          <t xml:space="preserve">transfer_open._default.normal[2]</t>
         </is>
       </c>
       <c r="F53" t="inlineStr" s="5">
@@ -1952,7 +1952,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.bold._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open._default.bold[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.bold._default[1]</t>
+          <t xml:space="preserve">transfer_open._default.bold[1]</t>
         </is>
       </c>
       <c r="F54" t="inlineStr" s="6">
@@ -1984,7 +1984,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.bold._default[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open._default.bold[2]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.bold._default[2]</t>
+          <t xml:space="preserve">transfer_open._default.bold[2]</t>
         </is>
       </c>
       <c r="F55" t="inlineStr" s="6">
@@ -2016,7 +2016,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.quiet._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open._default.quiet[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.quiet._default[1]</t>
+          <t xml:space="preserve">transfer_open._default.quiet[1]</t>
         </is>
       </c>
       <c r="F56" t="inlineStr" s="7">
@@ -2048,7 +2048,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.quiet._default[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open._default.quiet[2]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.quiet._default[2]</t>
+          <t xml:space="preserve">transfer_open._default.quiet[2]</t>
         </is>
       </c>
       <c r="F57" t="inlineStr" s="7">
@@ -2080,7 +2080,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.shy._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open._default.shy[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.shy._default[1]</t>
+          <t xml:space="preserve">transfer_open._default.shy[1]</t>
         </is>
       </c>
       <c r="F58" t="inlineStr" s="8">
@@ -2112,7 +2112,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.shy._default[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open._default.shy[2]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.shy._default[2]</t>
+          <t xml:space="preserve">transfer_open._default.shy[2]</t>
         </is>
       </c>
       <c r="F59" t="inlineStr" s="8">
@@ -2144,7 +2144,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.easygoing._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.easygoing._default[1]</t>
+          <t xml:space="preserve">transfer_open._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F60" t="inlineStr" s="9">
@@ -2176,7 +2176,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.easygoing._default[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.easygoing._default[2]</t>
+          <t xml:space="preserve">transfer_open._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F61" t="inlineStr" s="9">
@@ -2208,7 +2208,7 @@
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.earnest._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open._default.earnest[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.earnest._default[1]</t>
+          <t xml:space="preserve">transfer_open._default.earnest[1]</t>
         </is>
       </c>
       <c r="F62" t="inlineStr" s="10">
@@ -2240,7 +2240,7 @@
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.earnest._default[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open._default.earnest[2]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.earnest._default[2]</t>
+          <t xml:space="preserve">transfer_open._default.earnest[2]</t>
         </is>
       </c>
       <c r="F63" t="inlineStr" s="10">
@@ -2272,7 +2272,7 @@
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.emotional._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open._default.emotional[1]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.emotional._default[1]</t>
+          <t xml:space="preserve">transfer_open._default.emotional[1]</t>
         </is>
       </c>
       <c r="F64" t="inlineStr" s="10">
@@ -2304,7 +2304,7 @@
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.emotional._default[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open._default.emotional[2]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.emotional._default[2]</t>
+          <t xml:space="preserve">transfer_open._default.emotional[2]</t>
         </is>
       </c>
       <c r="F65" t="inlineStr" s="10">
@@ -2336,7 +2336,7 @@
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.normal._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept._default.normal[1]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.normal._default[1]</t>
+          <t xml:space="preserve">raise_accept._default.normal[1]</t>
         </is>
       </c>
       <c r="F66" t="inlineStr" s="5">
@@ -2368,7 +2368,7 @@
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.bold._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept._default.bold[1]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.bold._default[1]</t>
+          <t xml:space="preserve">raise_accept._default.bold[1]</t>
         </is>
       </c>
       <c r="F67" t="inlineStr" s="6">
@@ -2400,7 +2400,7 @@
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.quiet._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept._default.quiet[1]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.quiet._default[1]</t>
+          <t xml:space="preserve">raise_accept._default.quiet[1]</t>
         </is>
       </c>
       <c r="F68" t="inlineStr" s="7">
@@ -2432,7 +2432,7 @@
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.shy._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept._default.shy[1]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.shy._default[1]</t>
+          <t xml:space="preserve">raise_accept._default.shy[1]</t>
         </is>
       </c>
       <c r="F69" t="inlineStr" s="8">
@@ -2464,7 +2464,7 @@
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.easygoing._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.easygoing._default[1]</t>
+          <t xml:space="preserve">raise_accept._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F70" t="inlineStr" s="9">
@@ -2496,7 +2496,7 @@
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.earnest._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept._default.earnest[1]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.earnest._default[1]</t>
+          <t xml:space="preserve">raise_accept._default.earnest[1]</t>
         </is>
       </c>
       <c r="F71" t="inlineStr" s="10">
@@ -2528,7 +2528,7 @@
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.emotional._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept._default.emotional[1]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.emotional._default[1]</t>
+          <t xml:space="preserve">raise_accept._default.emotional[1]</t>
         </is>
       </c>
       <c r="F72" t="inlineStr" s="10">
@@ -2560,7 +2560,7 @@
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.normal._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept._default.normal[1]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.normal._default[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept._default.normal[1]</t>
         </is>
       </c>
       <c r="F73" t="inlineStr" s="5">
@@ -2592,7 +2592,7 @@
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.bold._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept._default.bold[1]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.bold._default[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept._default.bold[1]</t>
         </is>
       </c>
       <c r="F74" t="inlineStr" s="6">
@@ -2624,7 +2624,7 @@
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.quiet._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept._default.quiet[1]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.quiet._default[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept._default.quiet[1]</t>
         </is>
       </c>
       <c r="F75" t="inlineStr" s="7">
@@ -2656,7 +2656,7 @@
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.shy._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept._default.shy[1]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.shy._default[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept._default.shy[1]</t>
         </is>
       </c>
       <c r="F76" t="inlineStr" s="8">
@@ -2688,7 +2688,7 @@
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.easygoing._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.easygoing._default[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F77" t="inlineStr" s="9">
@@ -2720,7 +2720,7 @@
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.earnest._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept._default.earnest[1]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.earnest._default[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept._default.earnest[1]</t>
         </is>
       </c>
       <c r="F78" t="inlineStr" s="10">
@@ -2752,7 +2752,7 @@
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.emotional._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept._default.emotional[1]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.emotional._default[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept._default.emotional[1]</t>
         </is>
       </c>
       <c r="F79" t="inlineStr" s="10">
@@ -2784,7 +2784,7 @@
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.normal._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse._default.normal[1]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.normal._default[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse._default.normal[1]</t>
         </is>
       </c>
       <c r="F80" t="inlineStr" s="5">
@@ -2816,7 +2816,7 @@
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.bold._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse._default.bold[1]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.bold._default[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse._default.bold[1]</t>
         </is>
       </c>
       <c r="F81" t="inlineStr" s="6">
@@ -2848,7 +2848,7 @@
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.quiet._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse._default.quiet[1]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.quiet._default[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse._default.quiet[1]</t>
         </is>
       </c>
       <c r="F82" t="inlineStr" s="7">
@@ -2880,7 +2880,7 @@
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.shy._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse._default.shy[1]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.shy._default[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse._default.shy[1]</t>
         </is>
       </c>
       <c r="F83" t="inlineStr" s="8">
@@ -2912,7 +2912,7 @@
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.easygoing._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.easygoing._default[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F84" t="inlineStr" s="9">
@@ -2944,7 +2944,7 @@
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.earnest._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse._default.earnest[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.earnest._default[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse._default.earnest[1]</t>
         </is>
       </c>
       <c r="F85" t="inlineStr" s="10">
@@ -2976,7 +2976,7 @@
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.emotional._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse._default.emotional[1]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.emotional._default[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse._default.emotional[1]</t>
         </is>
       </c>
       <c r="F86" t="inlineStr" s="10">
@@ -3008,7 +3008,7 @@
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.normal._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse._default.normal[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.normal._default[1]</t>
+          <t xml:space="preserve">raise_refuse._default.normal[1]</t>
         </is>
       </c>
       <c r="F87" t="inlineStr" s="5">
@@ -3040,7 +3040,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.bold._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse._default.bold[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.bold._default[1]</t>
+          <t xml:space="preserve">raise_refuse._default.bold[1]</t>
         </is>
       </c>
       <c r="F88" t="inlineStr" s="6">
@@ -3072,7 +3072,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.quiet._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse._default.quiet[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.quiet._default[1]</t>
+          <t xml:space="preserve">raise_refuse._default.quiet[1]</t>
         </is>
       </c>
       <c r="F89" t="inlineStr" s="7">
@@ -3104,7 +3104,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.shy._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse._default.shy[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.shy._default[1]</t>
+          <t xml:space="preserve">raise_refuse._default.shy[1]</t>
         </is>
       </c>
       <c r="F90" t="inlineStr" s="8">
@@ -3136,7 +3136,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.easygoing._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.easygoing._default[1]</t>
+          <t xml:space="preserve">raise_refuse._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F91" t="inlineStr" s="9">
@@ -3168,7 +3168,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.earnest._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse._default.earnest[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.earnest._default[1]</t>
+          <t xml:space="preserve">raise_refuse._default.earnest[1]</t>
         </is>
       </c>
       <c r="F92" t="inlineStr" s="10">
@@ -3200,7 +3200,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.emotional._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse._default.emotional[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.emotional._default[1]</t>
+          <t xml:space="preserve">raise_refuse._default.emotional[1]</t>
         </is>
       </c>
       <c r="F93" t="inlineStr" s="10">
@@ -3232,7 +3232,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.normal._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success._default.normal[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.normal._default[1]</t>
+          <t xml:space="preserve">transfer_retain_success._default.normal[1]</t>
         </is>
       </c>
       <c r="F94" t="inlineStr" s="5">
@@ -3264,7 +3264,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.bold._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success._default.bold[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.bold._default[1]</t>
+          <t xml:space="preserve">transfer_retain_success._default.bold[1]</t>
         </is>
       </c>
       <c r="F95" t="inlineStr" s="6">
@@ -3296,7 +3296,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.quiet._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success._default.quiet[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.quiet._default[1]</t>
+          <t xml:space="preserve">transfer_retain_success._default.quiet[1]</t>
         </is>
       </c>
       <c r="F96" t="inlineStr" s="7">
@@ -3328,7 +3328,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.shy._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success._default.shy[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.shy._default[1]</t>
+          <t xml:space="preserve">transfer_retain_success._default.shy[1]</t>
         </is>
       </c>
       <c r="F97" t="inlineStr" s="8">
@@ -3360,7 +3360,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.easygoing._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.easygoing._default[1]</t>
+          <t xml:space="preserve">transfer_retain_success._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F98" t="inlineStr" s="9">
@@ -3392,7 +3392,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.earnest._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success._default.earnest[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.earnest._default[1]</t>
+          <t xml:space="preserve">transfer_retain_success._default.earnest[1]</t>
         </is>
       </c>
       <c r="F99" t="inlineStr" s="10">
@@ -3424,7 +3424,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.emotional._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success._default.emotional[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.emotional._default[1]</t>
+          <t xml:space="preserve">transfer_retain_success._default.emotional[1]</t>
         </is>
       </c>
       <c r="F100" t="inlineStr" s="10">
@@ -3456,7 +3456,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.normal._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail._default.normal[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.normal._default[1]</t>
+          <t xml:space="preserve">transfer_retain_fail._default.normal[1]</t>
         </is>
       </c>
       <c r="F101" t="inlineStr" s="5">
@@ -3488,7 +3488,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.bold._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail._default.bold[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.bold._default[1]</t>
+          <t xml:space="preserve">transfer_retain_fail._default.bold[1]</t>
         </is>
       </c>
       <c r="F102" t="inlineStr" s="6">
@@ -3520,7 +3520,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.quiet._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail._default.quiet[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.quiet._default[1]</t>
+          <t xml:space="preserve">transfer_retain_fail._default.quiet[1]</t>
         </is>
       </c>
       <c r="F103" t="inlineStr" s="7">
@@ -3552,7 +3552,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.shy._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail._default.shy[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.shy._default[1]</t>
+          <t xml:space="preserve">transfer_retain_fail._default.shy[1]</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="8">
@@ -3584,7 +3584,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.easygoing._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.easygoing._default[1]</t>
+          <t xml:space="preserve">transfer_retain_fail._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F105" t="inlineStr" s="9">
@@ -3616,7 +3616,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.earnest._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail._default.earnest[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.earnest._default[1]</t>
+          <t xml:space="preserve">transfer_retain_fail._default.earnest[1]</t>
         </is>
       </c>
       <c r="F106" t="inlineStr" s="10">
@@ -3648,7 +3648,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.emotional._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail._default.emotional[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.emotional._default[1]</t>
+          <t xml:space="preserve">transfer_retain_fail._default.emotional[1]</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="10">
@@ -3680,7 +3680,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.normal._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release._default.normal[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.normal._default[1]</t>
+          <t xml:space="preserve">transfer_release._default.normal[1]</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="5">
@@ -3712,7 +3712,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.bold._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release._default.bold[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.bold._default[1]</t>
+          <t xml:space="preserve">transfer_release._default.bold[1]</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="6">
@@ -3744,7 +3744,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.quiet._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release._default.quiet[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.quiet._default[1]</t>
+          <t xml:space="preserve">transfer_release._default.quiet[1]</t>
         </is>
       </c>
       <c r="F110" t="inlineStr" s="7">
@@ -3776,7 +3776,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.shy._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release._default.shy[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.shy._default[1]</t>
+          <t xml:space="preserve">transfer_release._default.shy[1]</t>
         </is>
       </c>
       <c r="F111" t="inlineStr" s="8">
@@ -3808,7 +3808,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.easygoing._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.easygoing._default[1]</t>
+          <t xml:space="preserve">transfer_release._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F112" t="inlineStr" s="9">
@@ -3840,7 +3840,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.earnest._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release._default.earnest[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.earnest._default[1]</t>
+          <t xml:space="preserve">transfer_release._default.earnest[1]</t>
         </is>
       </c>
       <c r="F113" t="inlineStr" s="10">
@@ -3872,7 +3872,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.emotional._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release._default.emotional[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.emotional._default[1]</t>
+          <t xml:space="preserve">transfer_release._default.emotional[1]</t>
         </is>
       </c>
       <c r="F114" t="inlineStr" s="10">
@@ -3904,7 +3904,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.normal._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen._default.normal[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.normal._default[1]</t>
+          <t xml:space="preserve">transfer_listen._default.normal[1]</t>
         </is>
       </c>
       <c r="F115" t="inlineStr" s="5">
@@ -3936,7 +3936,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.bold._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen._default.bold[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.bold._default[1]</t>
+          <t xml:space="preserve">transfer_listen._default.bold[1]</t>
         </is>
       </c>
       <c r="F116" t="inlineStr" s="6">
@@ -3968,7 +3968,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.quiet._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen._default.quiet[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.quiet._default[1]</t>
+          <t xml:space="preserve">transfer_listen._default.quiet[1]</t>
         </is>
       </c>
       <c r="F117" t="inlineStr" s="7">
@@ -4000,7 +4000,7 @@
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.shy._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen._default.shy[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.shy._default[1]</t>
+          <t xml:space="preserve">transfer_listen._default.shy[1]</t>
         </is>
       </c>
       <c r="F118" t="inlineStr" s="8">
@@ -4032,7 +4032,7 @@
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.easygoing._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.easygoing._default[1]</t>
+          <t xml:space="preserve">transfer_listen._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F119" t="inlineStr" s="9">
@@ -4064,7 +4064,7 @@
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.earnest._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen._default.earnest[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.earnest._default[1]</t>
+          <t xml:space="preserve">transfer_listen._default.earnest[1]</t>
         </is>
       </c>
       <c r="F120" t="inlineStr" s="10">
@@ -4096,7 +4096,7 @@
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.emotional._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen._default.emotional[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.emotional._default[1]</t>
+          <t xml:space="preserve">transfer_listen._default.emotional[1]</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="10">
@@ -4425,7 +4425,7 @@
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.bold._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure._default.bold[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.bold._default[1]</t>
+          <t xml:space="preserve">sudden_departure._default.bold[1]</t>
         </is>
       </c>
       <c r="F133" t="inlineStr" s="6">
@@ -4457,7 +4457,7 @@
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.bold._default[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure._default.bold[2]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.bold._default[2]</t>
+          <t xml:space="preserve">sudden_departure._default.bold[2]</t>
         </is>
       </c>
       <c r="F134" t="inlineStr" s="6">
@@ -4489,7 +4489,7 @@
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.bold._default[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure._default.bold[3]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.bold._default[3]</t>
+          <t xml:space="preserve">sudden_departure._default.bold[3]</t>
         </is>
       </c>
       <c r="F135" t="inlineStr" s="6">
@@ -4521,7 +4521,7 @@
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure._default.quiet[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4536,24 +4536,24 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.introverted.ojousama[1]</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">sudden_departure._default.quiet[1]</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……申し訳ありません。もう、限界ですの。……ごきげんよう。</t>
+          <t xml:space="preserve">……すみません。もう、限界なんです。……さようなら。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted.ojousama[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure._default.quiet[2]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4568,24 +4568,24 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.introverted.ojousama[2]</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">sudden_departure._default.quiet[2]</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ずっと堪えてまいりました。ですが、もう……。</t>
+          <t xml:space="preserve">……ずっと我慢してきたんです。でも、もう……。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure._default.quiet[3]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4600,24 +4600,24 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.introverted.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">sudden_departure._default.quiet[3]</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すんません。もう、限界っす。……さよなら。</t>
+          <t xml:space="preserve">……何も言わずに去ろうかと思ったけど、一応挨拶だけ。辞めます。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted.delinquent[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4632,24 +4632,24 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.introverted.delinquent[2]</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">sudden_departure._default.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……黙って出てこうかと思ったんすけど。一応、挨拶だけ。辞めます。</t>
+          <t xml:space="preserve">いやー、ついにこの日が来ちゃいましたね。じゃ、元気で。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4664,24 +4664,24 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.introverted.cool[1]</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">sudden_departure._default.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すみません。……もう、限界です</t>
+          <t xml:space="preserve">もう潮時かなって。楽しかったですよ、うん。じゃあね！</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted.cool[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure._default.easygoing[3]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.introverted.cool[2]</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">sudden_departure._default.easygoing[3]</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……黙って消えようかと思った。……一応、挨拶だけ</t>
+          <t xml:space="preserve">あはは、もう笑うしかないですよね。辞めまーす。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure._default.earnest[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4728,24 +4728,24 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.introverted.seductive[1]</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">sudden_departure._default.earnest[1]</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめんなさい。もう、限界なの。……さようなら。</t>
+          <t xml:space="preserve">社長、長い間お世話になりました。でも、もうここでは続けられません。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted.seductive[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure._default.earnest[2]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4760,24 +4760,24 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.introverted.seductive[2]</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">sudden_departure._default.earnest[2]</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ずっと黙って耐えてきたわ。でも、もう……。</t>
+          <t xml:space="preserve">自分なりにずっと考えてきました。……ここを去ることにします。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure._default.earnest[3]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4792,24 +4792,24 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.introverted.composed[1]</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">sudden_departure._default.earnest[3]</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すみません。…もう、限界でね。…さようなら。</t>
+          <t xml:space="preserve">これ以上、自分を偽って続けることはできません。退団させてください。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted.composed[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure._default.emotional[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4824,24 +4824,24 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.introverted.composed[2]</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">sudden_departure._default.emotional[1]</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…黙って出ていこうかと思ったけど。…一応、挨拶だけ。辞めます。</t>
+          <t xml:space="preserve">もういいです。もう何も言いたくない。……さよなら。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted._default[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure._default.emotional[2]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4856,19 +4856,24 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.introverted._default[1]</t>
+          <t xml:space="preserve">sudden_departure._default.emotional[2]</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すみません。もう、限界なんです。……さようなら。</t>
+          <t xml:space="preserve">なんで……なんでこんなことになったんですか。もう無理です、辞めます。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted._default[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure._default.emotional[3]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4883,19 +4888,24 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.introverted._default[2]</t>
+          <t xml:space="preserve">sudden_departure._default.emotional[3]</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ずっと我慢してきたんです。でも、もう……。</t>
+          <t xml:space="preserve">悔しい……悔しいけど、もうここにはいられない。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted._default[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure._default.shy[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -4910,19 +4920,24 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.introverted._default[3]</t>
+          <t xml:space="preserve">sudden_departure._default.shy[1]</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……何も言わずに去ろうかと思ったけど、一応挨拶だけ。辞めます。</t>
+          <t xml:space="preserve">……あの、辞め……辞めさせてください……。もう、無理なんです……。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure._default.shy[2]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -4937,24 +4952,24 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.introverted.polite[1]</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">sudden_departure._default.shy[2]</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……お忙しいところすみません。退団届を、出させてください。</t>
+          <t xml:space="preserve">……ごめんなさい。もう、ここにはいられません……。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.introverted.polite[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure._default.normal[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -4969,24 +4984,24 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.introverted.polite[2]</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">sudden_departure._default.normal[1]</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……色々考えたんですけど、もう続けられません。すみません。</t>
+          <t xml:space="preserve">社長、話は短く済ませます。辞めます。もう決めました。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure._default.normal[2]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5001,24 +5016,24 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.carefree.ojousama[1]</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">sudden_departure._default.normal[2]</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、とうとうこの日が参りましたのね。では、お元気で。</t>
+          <t xml:space="preserve">お世話になりました。でも、もうここでは続けられません。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree.ojousama[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure._default.normal[3]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5033,24 +5048,24 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.carefree.ojousama[2]</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">sudden_departure._default.normal[3]</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そろそろ潮時かしら。楽しゅうございました、ええ。ごきげんよう。</t>
+          <t xml:space="preserve">色々ありましたけど……もう、終わりにします。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree.delinquent[1]</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.composed[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5060,29 +5075,29 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.carefree.delinquent[1]</t>
+          <t xml:space="preserve">composed[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー、ついにこの日が来ちまったっすね。じゃ、元気で。</t>
+          <t xml:space="preserve">……短い間だったけど、悪くない時間だった。ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree.delinquent[2]</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.composed[2]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5092,29 +5107,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.carefree.delinquent[2]</t>
+          <t xml:space="preserve">composed[2]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう潮時っしょ。楽しかったっすよ、うん。じゃあ、失礼します。</t>
+          <t xml:space="preserve">ま、こういうこともあるよね。……元気でね、社長。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree.cool[1]</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.composed[3]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5124,29 +5139,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.carefree.cool[1]</t>
+          <t xml:space="preserve">composed[3]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ついに、この日か。……じゃ、元気で</t>
+          <t xml:space="preserve">……わかった。世話になったよ。次の場所、自分で見つけるから。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree.cool[2]</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.ojousama[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5156,29 +5171,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.carefree.cool[2]</t>
+          <t xml:space="preserve">ojousama[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…潮時だ。楽しかったよ。……辞めます</t>
+          <t xml:space="preserve">ご縁がここまでだったということですわね。お世話になりました。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree.polite[1]</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.ojousama[2]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5188,29 +5203,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.carefree.polite[1]</t>
+          <t xml:space="preserve">ojousama[2]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー、ついにこの日が来てしまいましたね。では、お元気で。</t>
+          <t xml:space="preserve">……承知いたしましたわ。これまでのご厚情、忘れませんわ。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree.polite[2]</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.ojousama[3]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5220,29 +5235,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.carefree.polite[2]</t>
+          <t xml:space="preserve">ojousama[3]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう潮時かなと思いまして。楽しかったですよ、ええ。失礼します！</t>
+          <t xml:space="preserve">わたくしの居場所は、また別にございますわ。社長もお元気で。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree.composed[1]</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.polite[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5252,29 +5267,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.carefree.composed[1]</t>
+          <t xml:space="preserve">polite[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いやあ、ついにこの日が来たね。…じゃ、元気で。</t>
+          <t xml:space="preserve">至らない点があったなら、申し訳ありませんでした。今までご指導ありがとうございました。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree.composed[2]</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.polite[2]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5284,29 +5299,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.carefree.composed[2]</t>
+          <t xml:space="preserve">polite[2]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…潮時かなって。楽しかったよ、うん。…じゃあね。</t>
+          <t xml:space="preserve">力不足でした。……この経験を、次に必ず活かさせていただきます。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree._default[1]</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.polite[3]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5316,24 +5331,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.carefree._default[1]</t>
+          <t xml:space="preserve">polite[3]</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー、ついにこの日が来ちゃいましたね。じゃ、元気で。</t>
+          <t xml:space="preserve">お世話になりました。社長も、団体の皆様も、どうかお元気で。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree._default[2]</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.seductive[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5343,24 +5363,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.carefree._default[2]</t>
+          <t xml:space="preserve">seductive[1]</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう潮時かなって。楽しかったですよ、うん。じゃあね！</t>
+          <t xml:space="preserve">あら、寂しいことを仰るのね。……ふふ、いいわ、潔く出ていきましょう。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree._default[3]</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.seductive[2]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5370,24 +5395,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.carefree._default[3]</t>
+          <t xml:space="preserve">seductive[2]</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、もう笑うしかないですよね。辞めまーす。</t>
+          <t xml:space="preserve">別れって、嫌いじゃないの。……お世話になったわ、社長。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree.seductive[1]</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.seductive[3]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5397,12 +5427,12 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.carefree.seductive[1]</t>
+          <t xml:space="preserve">seductive[3]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5412,14 +5442,14 @@
       </c>
       <c r="G164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、もう引き止めないでくださいね？ 決めちゃったんですから。</t>
+          <t xml:space="preserve">またどこかで会えるかしら。……忘れないでね、私のこと。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.carefree.seductive[2]</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.delinquent[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5429,29 +5459,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.carefree.seductive[2]</t>
+          <t xml:space="preserve">delinquent[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さよなら、社長。楽しかった時もあったわ。</t>
+          <t xml:space="preserve">チッ……悔しいけど、次はもっといい場所で暴れてやるよ。見てな。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest._default[1]</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.delinquent[2]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5461,29 +5491,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.earnest._default[1]</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、長い間お世話になりました。でも、もうここでは続けられません。</t>
+          <t xml:space="preserve">こうなったらどこ行っても結果出すからな。覚えとけよ社長。</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest._default[2]</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.delinquent[3]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5493,29 +5523,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.earnest._default[2]</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">delinquent[3]</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">自分なりにずっと考えてきました。……ここを去ることにします。</t>
+          <t xml:space="preserve">……わかったよ。この悔しさ、絶対に忘れねぇからな。</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest._default[3]</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.cool[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5525,29 +5555,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.earnest._default[3]</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">cool[1]</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これ以上、自分を偽って続けることはできません。退団させてください。</t>
+          <t xml:space="preserve">……わかった。</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.emotional._default[1]</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.cool[2]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5557,29 +5587,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.emotional._default[1]</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">cool[2]</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もういいです。もう何も言いたくない。……さよなら。</t>
+          <t xml:space="preserve">……世話になった。</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.emotional._default[2]</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.cool[3]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5589,29 +5619,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.emotional._default[2]</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">cool[3]</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんで……なんでこんなことになったんですか。もう無理です、辞めます。</t>
+          <t xml:space="preserve">……次の場所で、結果を出す。</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.emotional._default[3]</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.standard[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5621,29 +5651,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.emotional._default[3]</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">standard[1]</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい……悔しいけど、もうここにはいられない。</t>
+          <t xml:space="preserve">短い間でしたが、ありがとうございました。</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.shy._default[1]</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.standard[2]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5653,29 +5683,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.shy._default[1]</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">standard[2]</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの、辞め……辞めさせてください……。もう、無理なんです……。</t>
+          <t xml:space="preserve">色々と、お世話になりました。……お元気で。</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.shy._default[2]</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.standard[3]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5685,795 +5715,27 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.shy._default[2]</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">standard[3]</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめんなさい。もう、ここにはいられません……。</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="40" customHeight="1">
-      <c r="A174" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal._default[1]</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">sudden_departure.normal._default[1]</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、話は短く済ませます。辞めます。もう決めました。</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="40" customHeight="1">
-      <c r="A175" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal._default[2]</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">sudden_departure.normal._default[2]</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">お世話になりました。でも、もうここでは続けられません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="40" customHeight="1">
-      <c r="A176" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.normal._default[3]</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">sudden_departure.normal._default[3]</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">色々ありましたけど……もう、終わりにします。</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="40" customHeight="1">
-      <c r="A177" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.composed[1]</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">composed[1]</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">……短い間だったけど、悪くない時間だった。ありがとう。</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="40" customHeight="1">
-      <c r="A178" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.composed[2]</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">composed[2]</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ま、こういうこともあるよね。……元気でね、社長。</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="40" customHeight="1">
-      <c r="A179" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.composed[3]</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">composed[3]</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">鷹揚</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">……わかった。世話になったよ。次の場所、自分で見つけるから。</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="40" customHeight="1">
-      <c r="A180" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.ojousama[1]</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ojousama[1]</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ご縁がここまでだったということですわね。お世話になりました。</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="40" customHeight="1">
-      <c r="A181" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.ojousama[2]</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ojousama[2]</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">……承知いたしましたわ。これまでのご厚情、忘れませんわ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="40" customHeight="1">
-      <c r="A182" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.ojousama[3]</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ojousama[3]</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">お嬢様</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">わたくしの居場所は、また別にございますわ。社長もお元気で。</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="40" customHeight="1">
-      <c r="A183" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.polite[1]</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">polite[1]</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">至らない点があったなら、申し訳ありませんでした。今までご指導ありがとうございました。</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="40" customHeight="1">
-      <c r="A184" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.polite[2]</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">polite[2]</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">力不足でした。……この経験を、次に必ず活かさせていただきます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="40" customHeight="1">
-      <c r="A185" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.polite[3]</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">polite[3]</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">丁寧</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">お世話になりました。社長も、団体の皆様も、どうかお元気で。</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="40" customHeight="1">
-      <c r="A186" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.seductive[1]</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">seductive[1]</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">あら、寂しいことを仰るのね。……ふふ、いいわ、潔く出ていきましょう。</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="40" customHeight="1">
-      <c r="A187" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.seductive[2]</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">seductive[2]</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">別れって、嫌いじゃないの。……お世話になったわ、社長。</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" ht="40" customHeight="1">
-      <c r="A188" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.seductive[3]</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">seductive[3]</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">蠱惑</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">またどこかで会えるかしら。……忘れないでね、私のこと。</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="40" customHeight="1">
-      <c r="A189" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.delinquent[1]</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">delinquent[1]</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">チッ……悔しいけど、次はもっといい場所で暴れてやるよ。見てな。</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="40" customHeight="1">
-      <c r="A190" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.delinquent[2]</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">delinquent[2]</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">こうなったらどこ行っても結果出すからな。覚えとけよ社長。</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="40" customHeight="1">
-      <c r="A191" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.delinquent[3]</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">delinquent[3]</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ヤンキー</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">……わかったよ。この悔しさ、絶対に忘れねぇからな。</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="40" customHeight="1">
-      <c r="A192" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.cool[1]</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">cool[1]</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">……わかった。</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="40" customHeight="1">
-      <c r="A193" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.cool[2]</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">cool[2]</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">……世話になった。</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="40" customHeight="1">
-      <c r="A194" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.cool[3]</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">cool[3]</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">クール</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">……次の場所で、結果を出す。</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="40" customHeight="1">
-      <c r="A195" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.standard[1]</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">standard[1]</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">標準</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">短い間でしたが、ありがとうございました。</t>
-        </is>
-      </c>
-    </row>
-    <row r="196" ht="40" customHeight="1">
-      <c r="A196" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.standard[2]</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">standard[2]</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">標準</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">色々と、お世話になりました。……お元気で。</t>
-        </is>
-      </c>
-    </row>
-    <row r="197" ht="40" customHeight="1">
-      <c r="A197" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.standard[3]</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">standard[3]</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">標準</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr" s="3">
-        <is>
           <t xml:space="preserve">これからも、この団体の活躍、祈ってます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I197"/>
+  <autoFilter ref="A1:I173"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/その他セリフ/06-契約交渉.xlsx
+++ b/セリフ編集/その他セリフ/06-契約交渉.xlsx
@@ -192,7 +192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I99"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -256,7 +256,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.1</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.1.standard</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -271,7 +271,12 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">tenure.1</t>
+          <t xml:space="preserve">tenure.1.standard</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G2" t="inlineStr" s="3">
@@ -283,7 +288,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.short</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.1.composed</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -298,19 +303,24 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">tenure.short</t>
+          <t xml:space="preserve">tenure.1.composed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G3" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここで過ごした{n}年間、</t>
+          <t xml:space="preserve">…まだ1年だけどね、</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.long</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.1.ojousama</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -325,19 +335,24 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">tenure.long</t>
+          <t xml:space="preserve">tenure.1.ojousama</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G4" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう{n}年になるんですね……。</t>
+          <t xml:space="preserve">まだ一年ですけれど、</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.founder</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.1.delinquent</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -352,19 +367,24 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">tenure.founder</t>
+          <t xml:space="preserve">tenure.1.delinquent</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G5" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">旗揚げからここにいるんですよ、私。</t>
+          <t xml:space="preserve">まだ1年だけどよ、</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.ace</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.1.cool</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -379,19 +399,24 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">record.ace</t>
+          <t xml:space="preserve">tenure.1.cool</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G6" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体で一番やれてる自信はあります。それは数字にも出てるはずです。</t>
+          <t xml:space="preserve">……まだ1年。それでも、</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.good</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.1.seductive</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -406,19 +431,24 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">record.good</t>
+          <t xml:space="preserve">tenure.1.seductive</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G7" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">自分なりに結果は出してきたつもりです。</t>
+          <t xml:space="preserve">まだ一年だけれど、</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.developing</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.1.polite</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -433,19 +463,24 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">record.developing</t>
+          <t xml:space="preserve">tenure.1.polite</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G8" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ発展途上なのはわかってます。でも、ちゃんと見てほしいんです。</t>
+          <t xml:space="preserve">まだ1年ですけれど、</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.few_matches</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.short.standard</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -460,19 +495,24 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">record.few_matches</t>
+          <t xml:space="preserve">tenure.short.standard</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G9" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あんまり試合に出してもらえなかった……。</t>
+          <t xml:space="preserve">ここで過ごした{n}年間、</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.rivalry.has_rival</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.short.composed</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -487,19 +527,24 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry.has_rival</t>
+          <t xml:space="preserve">tenure.short.composed</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G10" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{rivalName}とまだ決着ついてないけど……もういいです。</t>
+          <t xml:space="preserve">…ここで過ごした{n}年ね、</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure_farewell.long</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.short.ojousama</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -514,19 +559,24 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">tenure_farewell.long</t>
+          <t xml:space="preserve">tenure.short.ojousama</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G11" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここで過ごした{n}年間、無駄じゃなかったって思いたいです。</t>
+          <t xml:space="preserve">この団体で過ごした{n}年、</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure_farewell.founder</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.short.delinquent</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -541,19 +591,24 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">tenure_farewell.founder</t>
+          <t xml:space="preserve">tenure.short.delinquent</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G12" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">旗揚げの時からいたんだな……なんか、不思議。</t>
+          <t xml:space="preserve">ここで{n}年やってきて、</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.short.cool</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -563,29 +618,29 @@
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed[1]</t>
+          <t xml:space="preserve">tenure.short.cool</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G13" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……短い間だったけど、悪くない時間だった。ありがとう。</t>
+          <t xml:space="preserve">……ここでの{n}年。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.composed[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.short.seductive</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -595,29 +650,29 @@
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed[2]</t>
+          <t xml:space="preserve">tenure.short.seductive</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G14" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、こういうこともあるよね。……元気でね、社長。</t>
+          <t xml:space="preserve">ここで過ごした{n}年、</t>
         </is>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.composed[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.short.polite</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -627,29 +682,29 @@
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed[3]</t>
+          <t xml:space="preserve">tenure.short.polite</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">鷹揚</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G15" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……わかった。世話になったよ。次の場所、自分で見つけるから。</t>
+          <t xml:space="preserve">ここで過ごさせていただいた{n}年間、</t>
         </is>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.long.standard</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -659,29 +714,29 @@
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama[1]</t>
+          <t xml:space="preserve">tenure.long.standard</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G16" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ご縁がここまでだったということですわね。お世話になりました。</t>
+          <t xml:space="preserve">もう{n}年になるんですね……。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.ojousama[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.long.composed</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -691,29 +746,29 @@
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama[2]</t>
+          <t xml:space="preserve">tenure.long.composed</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お嬢様</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G17" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……承知いたしましたわ。これまでのご厚情、忘れませんわ。</t>
+          <t xml:space="preserve">…もう{n}年か。早いね。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.ojousama[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.long.ojousama</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -723,12 +778,12 @@
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama[3]</t>
+          <t xml:space="preserve">tenure.long.ojousama</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -738,14 +793,14 @@
       </c>
       <c r="G18" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしの居場所は、また別にございますわ。社長もお元気で。</t>
+          <t xml:space="preserve">もう{n}年になりますのね……。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.long.delinquent</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -755,29 +810,29 @@
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite[1]</t>
+          <t xml:space="preserve">tenure.long.delinquent</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">ヤンキー</t>
         </is>
       </c>
       <c r="G19" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">至らない点があったなら、申し訳ありませんでした。今までご指導ありがとうございました。</t>
+          <t xml:space="preserve">もう{n}年か……早ぇもんだな。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.polite[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.long.cool</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -787,29 +842,29 @@
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite[2]</t>
+          <t xml:space="preserve">tenure.long.cool</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G20" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">力不足でした。……この経験を、次に必ず活かさせていただきます。</t>
+          <t xml:space="preserve">……もう{n}年。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.polite[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.long.seductive</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -819,29 +874,29 @@
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite[3]</t>
+          <t xml:space="preserve">tenure.long.seductive</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">丁寧</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G21" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お世話になりました。社長も、団体の皆様も、どうかお元気で。</t>
+          <t xml:space="preserve">もう{n}年になるのね……。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.long.polite</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -851,29 +906,29 @@
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive[1]</t>
+          <t xml:space="preserve">tenure.long.polite</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G22" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、寂しいことを仰るのね。……ふふ、いいわ、潔く出ていきましょう。</t>
+          <t xml:space="preserve">もう{n}年になるのですね……。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.seductive[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.founder.standard</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -883,29 +938,29 @@
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive[2]</t>
+          <t xml:space="preserve">tenure.founder.standard</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G23" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">別れって、嫌いじゃないの。……お世話になったわ、社長。</t>
+          <t xml:space="preserve">旗揚げからここにいるんですよ、私。</t>
         </is>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.seductive[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.founder.composed</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -915,29 +970,29 @@
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive[3]</t>
+          <t xml:space="preserve">tenure.founder.composed</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">蠱惑</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G24" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">またどこかで会えるかしら。……忘れないでね、私のこと。</t>
+          <t xml:space="preserve">…旗揚げからずっとここにいるんだよ、私。</t>
         </is>
       </c>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.delinquent[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.founder.ojousama</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -947,29 +1002,29 @@
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent[1]</t>
+          <t xml:space="preserve">tenure.founder.ojousama</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G25" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チッ……悔しいけど、次はもっといい場所で暴れてやるよ。見てな。</t>
+          <t xml:space="preserve">旗揚げの時からここにおりますのよ、わたくし。</t>
         </is>
       </c>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.delinquent[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.founder.delinquent</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -979,12 +1034,12 @@
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent[2]</t>
+          <t xml:space="preserve">tenure.founder.delinquent</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -994,14 +1049,14 @@
       </c>
       <c r="G26" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こうなったらどこ行っても結果出すからな。覚えとけよ社長。</t>
+          <t xml:space="preserve">旗揚げからここにいるんだぜ、あたし。</t>
         </is>
       </c>
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.delinquent[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.founder.cool</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1011,29 +1066,29 @@
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">delinquent[3]</t>
+          <t xml:space="preserve">tenure.founder.cool</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ヤンキー</t>
+          <t xml:space="preserve">クール</t>
         </is>
       </c>
       <c r="G27" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……わかったよ。この悔しさ、絶対に忘れねぇからな。</t>
+          <t xml:space="preserve">……旗揚げから、ここにいる。</t>
         </is>
       </c>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.cool[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.founder.seductive</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1043,29 +1098,29 @@
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool[1]</t>
+          <t xml:space="preserve">tenure.founder.seductive</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">蠱惑</t>
         </is>
       </c>
       <c r="G28" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……わかった。</t>
+          <t xml:space="preserve">旗揚げからここにいるのよ、わたし。</t>
         </is>
       </c>
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.cool[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure.founder.polite</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1075,29 +1130,29 @@
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool[2]</t>
+          <t xml:space="preserve">tenure.founder.polite</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">丁寧</t>
         </is>
       </c>
       <c r="G29" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……世話になった。</t>
+          <t xml:space="preserve">旗揚げの時からここにおります、私。</t>
         </is>
       </c>
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.cool[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.ace.standard</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1107,29 +1162,29 @@
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cool[3]</t>
+          <t xml:space="preserve">record.ace.standard</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クール</t>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G30" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次の場所で、結果を出す。</t>
+          <t xml:space="preserve">この団体で一番やれてる自信はあります。それは数字にも出てるはずです。</t>
         </is>
       </c>
     </row>
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.standard[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.ace.composed</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1139,29 +1194,29 @@
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard[1]</t>
+          <t xml:space="preserve">record.ace.composed</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">鷹揚</t>
         </is>
       </c>
       <c r="G31" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間でしたが、ありがとうございました。</t>
+          <t xml:space="preserve">…この団体で一番やれてると思うよ。数字にも出てるはずだけどね。</t>
         </is>
       </c>
     </row>
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.standard[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.ace.ojousama</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1171,59 +1226,2171 @@
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard[2]</t>
+          <t xml:space="preserve">record.ace.ojousama</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">標準</t>
+          <t xml:space="preserve">お嬢様</t>
         </is>
       </c>
       <c r="G32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">色々と、お世話になりました。……お元気で。</t>
+          <t xml:space="preserve">この団体で最も結果を出している自負がございます。数字もそう示しているはずです。</t>
         </is>
       </c>
     </row>
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.ace.delinquent</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">record.ace.delinquent</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この団体で一番やれてる自信はある。数字にも出てんだろ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.ace.cool</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">record.ace.cool</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……この団体で一番やれてる。数字にも出てる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.ace.seductive</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">record.ace.seductive</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この団体で一番やれてる自信はあるの。数字も、そう言ってくれてるでしょう?</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="40" customHeight="1">
+      <c r="A36" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.ace.polite</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">record.ace.polite</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この団体で一番やれている自信があります。数字にも出ているはずです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.good.standard</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">record.good.standard</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">自分なりに結果は出してきたつもりです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.good.composed</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">record.good.composed</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…自分なりに、結果は出してきたつもりだよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.good.ojousama</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">record.good.ojousama</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたくしなりに、結果は出してまいりました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="40" customHeight="1">
+      <c r="A40" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.good.delinquent</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">record.good.delinquent</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あたしなりに結果は出してきたつもりだ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.good.cool</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">record.good.cool</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……自分なりに、結果は出した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.good.seductive</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">record.good.seductive</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたしなりに、結果は出してきたつもりよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.good.polite</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">record.good.polite</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">自分なりに結果は出してきたつもりです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.developing.standard</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">record.developing.standard</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ発展途上なのはわかってます。でも、ちゃんと見てほしいんです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="40" customHeight="1">
+      <c r="A45" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.developing.composed</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">record.developing.composed</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…まだ途中なのはわかってる。でも、見ていてほしいんだ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.developing.ojousama</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">record.developing.ojousama</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ道半ばなのは承知しております。それでも、見ていてくださいまし。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="40" customHeight="1">
+      <c r="A47" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.developing.delinquent</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">record.developing.delinquent</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ途中なのはわかってる。けど、ちゃんと見といてくれよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="40" customHeight="1">
+      <c r="A48" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.developing.cool</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">record.developing.cool</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……まだ途中。それでも、見ていてほしい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="40" customHeight="1">
+      <c r="A49" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.developing.seductive</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">record.developing.seductive</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ途中なのはわかってるの。でも、見ていてほしいのよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="40" customHeight="1">
+      <c r="A50" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.developing.polite</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">record.developing.polite</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ発展途上なのは承知しています。それでも、見ていてほしいのです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="40" customHeight="1">
+      <c r="A51" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.few_matches.standard</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">record.few_matches.standard</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あんまり試合に出してもらえなかった……。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="40" customHeight="1">
+      <c r="A52" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.few_matches.composed</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">record.few_matches.composed</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…あんまり試合、もらえなかったね……。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="40" customHeight="1">
+      <c r="A53" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.few_matches.ojousama</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">record.few_matches.ojousama</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あまり試合をいただけませんでした……。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="40" customHeight="1">
+      <c r="A54" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.few_matches.delinquent</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">record.few_matches.delinquent</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あんまり試合、回してもらえなかったな……。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="40" customHeight="1">
+      <c r="A55" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.few_matches.cool</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">record.few_matches.cool</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……試合、あまりもらえなかった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="40" customHeight="1">
+      <c r="A56" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.few_matches.seductive</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">record.few_matches.seductive</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あまり試合に出してもらえなかったわ……。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="40" customHeight="1">
+      <c r="A57" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.record.few_matches.polite</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">record.few_matches.polite</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あまり試合に出していただけませんでした……。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="40" customHeight="1">
+      <c r="A58" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.rivalry.has_rival.standard</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry.has_rival.standard</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">{rivalName}とまだ決着ついてないけど……もういいです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="40" customHeight="1">
+      <c r="A59" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.rivalry.has_rival.composed</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry.has_rival.composed</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…{rivalName}とはまだ決着がついてないけど、もういいんだ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="40" customHeight="1">
+      <c r="A60" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.rivalry.has_rival.ojousama</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry.has_rival.ojousama</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">{rivalName}とはまだ決着がついておりませんが……もう、よろしいのです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="40" customHeight="1">
+      <c r="A61" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.rivalry.has_rival.delinquent</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry.has_rival.delinquent</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">{rivalName}とはまだ決着ついてねぇけど……もういい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="40" customHeight="1">
+      <c r="A62" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.rivalry.has_rival.cool</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry.has_rival.cool</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……{rivalName}とは、まだ決着がついてない。でも、もういい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="40" customHeight="1">
+      <c r="A63" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.rivalry.has_rival.seductive</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry.has_rival.seductive</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">{rivalName}とはまだ決着がついてないけれど……もういいの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="40" customHeight="1">
+      <c r="A64" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.rivalry.has_rival.polite</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry.has_rival.polite</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">{rivalName}とはまだ決着がついていませんが……もう、いいのです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="40" customHeight="1">
+      <c r="A65" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure_farewell.long.standard</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">tenure_farewell.long.standard</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここで過ごした{n}年間、無駄じゃなかったって思いたいです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="40" customHeight="1">
+      <c r="A66" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure_farewell.long.composed</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">tenure_farewell.long.composed</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ここで過ごした{n}年、無駄じゃなかったと思いたいな。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="40" customHeight="1">
+      <c r="A67" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure_farewell.long.ojousama</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">tenure_farewell.long.ojousama</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここで過ごした{n}年、無駄ではなかったと思いたいのです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="40" customHeight="1">
+      <c r="A68" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure_farewell.long.delinquent</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">tenure_farewell.long.delinquent</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここで過ごした{n}年、無駄じゃなかったと思いてぇ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="40" customHeight="1">
+      <c r="A69" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure_farewell.long.cool</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">tenure_farewell.long.cool</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ここでの{n}年。無駄じゃなかったと思いたい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="40" customHeight="1">
+      <c r="A70" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure_farewell.long.seductive</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">tenure_farewell.long.seductive</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここで過ごした{n}年、無駄じゃなかったと思いたいわ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="40" customHeight="1">
+      <c r="A71" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure_farewell.long.polite</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">tenure_farewell.long.polite</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここで過ごさせていただいた{n}年間、無駄ではなかったと思いたいです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="40" customHeight="1">
+      <c r="A72" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure_farewell.founder.standard</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">tenure_farewell.founder.standard</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">旗揚げの時からいたんだな……なんか、不思議。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="40" customHeight="1">
+      <c r="A73" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure_farewell.founder.composed</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">tenure_farewell.founder.composed</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…旗揚げの時からいたんだね。なんだか、不思議だな。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="40" customHeight="1">
+      <c r="A74" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure_farewell.founder.ojousama</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">tenure_farewell.founder.ojousama</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">旗揚げの時からおりましたのね……なんだか、不思議です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="40" customHeight="1">
+      <c r="A75" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure_farewell.founder.delinquent</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">tenure_farewell.founder.delinquent</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">旗揚げの時からいたんだな……なんか、不思議だぜ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="40" customHeight="1">
+      <c r="A76" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure_farewell.founder.cool</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">tenure_farewell.founder.cool</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……旗揚げから、いた。なんだか、不思議。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="40" customHeight="1">
+      <c r="A77" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure_farewell.founder.seductive</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">tenure_farewell.founder.seductive</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">旗揚げの時からいたのね……なんだか、不思議だわ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="40" customHeight="1">
+      <c r="A78" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.tenure_farewell.founder.polite</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">tenure_farewell.founder.polite</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">旗揚げの時からおりました……なんだか、不思議です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="40" customHeight="1">
+      <c r="A79" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.composed[1]</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed[1]</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……短い間だったけど、悪くない時間だった。ありがとう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="40" customHeight="1">
+      <c r="A80" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.composed[2]</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed[2]</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ま、こういうこともあるよね。……元気でね、社長。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="40" customHeight="1">
+      <c r="A81" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.composed[3]</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed[3]</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">鷹揚</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……わかった。世話になったよ。次の場所、自分で見つけるから。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="40" customHeight="1">
+      <c r="A82" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ご縁がここまでだったということですわね。お世話になりました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="40" customHeight="1">
+      <c r="A83" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……承知いたしましたわ。これまでのご厚情、忘れませんわ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="40" customHeight="1">
+      <c r="A84" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.ojousama[3]</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama[3]</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">お嬢様</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたくしの居場所は、また別にございますわ。社長もお元気で。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="40" customHeight="1">
+      <c r="A85" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.polite[1]</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite[1]</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">至らない点があったなら、申し訳ありませんでした。今までご指導ありがとうございました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="40" customHeight="1">
+      <c r="A86" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.polite[2]</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite[2]</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">力不足でした。……この経験を、次に必ず活かさせていただきます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="40" customHeight="1">
+      <c r="A87" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.polite[3]</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite[3]</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">丁寧</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お世話になりました。社長も、団体の皆様も、どうかお元気で。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="40" customHeight="1">
+      <c r="A88" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive[1]</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、寂しいことを仰るのね。……ふふ、いいわ、潔く出ていきましょう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="40" customHeight="1">
+      <c r="A89" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive[2]</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">別れって、嫌いじゃないの。……お世話になったわ、社長。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="40" customHeight="1">
+      <c r="A90" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.seductive[3]</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive[3]</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">蠱惑</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">またどこかで会えるかしら。……忘れないでね、私のこと。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="40" customHeight="1">
+      <c r="A91" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.delinquent[1]</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent[1]</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">チッ……悔しいけど、次はもっといい場所で暴れてやるよ。見てな。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="40" customHeight="1">
+      <c r="A92" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.delinquent[2]</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent[2]</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">こうなったらどこ行っても結果出すからな。覚えとけよ社長。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="40" customHeight="1">
+      <c r="A93" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.delinquent[3]</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">delinquent[3]</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ヤンキー</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……わかったよ。この悔しさ、絶対に忘れねぇからな。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="40" customHeight="1">
+      <c r="A94" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.cool[1]</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool[1]</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……わかった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="40" customHeight="1">
+      <c r="A95" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.cool[2]</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool[2]</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……世話になった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="40" customHeight="1">
+      <c r="A96" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.cool[3]</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">cool[3]</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クール</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……次の場所で、結果を出す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="40" customHeight="1">
+      <c r="A97" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.standard[1]</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard[1]</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">短い間でしたが、ありがとうございました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="40" customHeight="1">
+      <c r="A98" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES.standard[2]</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard[2]</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">色々と、お世話になりました。……お元気で。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="40" customHeight="1">
+      <c r="A99" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">RELEASE_INTERVIEW_LINES.standard[3]</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr" s="2">
+      <c r="B99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">RELEASE_INTERVIEW_LINES</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr" s="12">
+      <c r="D99" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">standard[3]</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr" s="2">
+      <c r="E99" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">標準</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr" s="3">
+      <c r="G99" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">これからも、この団体の活躍、祈ってます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I33"/>
+  <autoFilter ref="A1:I99"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
